--- a/docs/downloads/20260901_Ukay_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/20260901_Ukay_Teduh_Weekly_Update.xlsx
@@ -493,7 +493,7 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
